--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_12t.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_12t.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F62409F-9603-4DA5-9B1D-D023D6426566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F9342DC-2653-469B-9672-AF875CDA0311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -573,10 +573,10 @@
     <t>day_night</t>
   </si>
   <si>
-    <t>RaP,RaD,WaD,WaP,FaD,FaP,SaP,SaD</t>
-  </si>
-  <si>
-    <t>RaN,RaP,SaN,WaN,FaN,WaP,FaP,SaP</t>
+    <t>FaP,SaP,RaP,FaD,RaD,SaD,WaD,WaP</t>
+  </si>
+  <si>
+    <t>RaP,FaN,FaP,SaP,SaN,WaN,RaN,WaP</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>RaN,RaP,SaN,WaN,FaN,WaP,FaP,SaP</v>
+        <v>RaP,FaN,FaP,SaP,SaN,WaN,RaN,WaP</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>RaP,RaD,WaD,WaP,FaD,FaP,SaP,SaD</v>
+        <v>FaP,SaP,RaP,FaD,RaD,SaD,WaD,WaP</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1299,7 +1299,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E3AC7BA-1677-49CA-BACA-A936B90A3B1D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C53F5EA4-4A0E-4295-9C12-382ADAEE6F5E}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1383,7 +1383,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09B60260-B616-4A42-A43A-5458DFB3CFEE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7806ABE4-6E32-4924-9283-3E0C76534E08}">
   <dimension ref="B9:O250"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9125,7 +9125,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5CA814D-5B34-42EB-A291-1A1A11D9A506}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6A2055D-9D5F-4132-8AFB-9CE1275E7237}">
   <dimension ref="B9:BL60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14338,7 +14338,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CAD9D68-5015-434B-A3E7-9AC1F8B04102}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B7C5AE9-2DC3-471C-8E6E-81F00BBEB232}">
   <dimension ref="B9:E22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14536,7 +14536,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9622CFF4-92B4-4426-814A-64F12975418C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6091837-A2DF-45B5-BFD7-55485AB3D7E7}">
   <dimension ref="B9:D34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14827,7 +14827,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95D9424C-A7D0-4D0C-A1DD-BACB78D2E2A4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A211BC48-ED2B-4482-BF99-F15C3F4D0E7D}">
   <dimension ref="B9:D22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14986,7 +14986,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C148502-2A20-4F86-93E1-EB8AA423FC8C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D765A33-264F-4635-906C-AF3940EC8E99}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15018,7 +15018,7 @@
         <v>37</v>
       </c>
       <c r="D11">
-        <v>0.19109999999999996</v>
+        <v>0.19110000000000002</v>
       </c>
       <c r="E11" t="s">
         <v>184</v>
@@ -15214,7 +15214,7 @@
         <v>43</v>
       </c>
       <c r="D25">
-        <v>0.2446666666666667</v>
+        <v>0.24466666666666667</v>
       </c>
       <c r="E25" t="s">
         <v>184</v>
@@ -15522,7 +15522,7 @@
         <v>37</v>
       </c>
       <c r="D47">
-        <v>0.24780000000000002</v>
+        <v>0.24779999999999999</v>
       </c>
       <c r="E47" t="s">
         <v>184</v>
@@ -15578,7 +15578,7 @@
         <v>37</v>
       </c>
       <c r="D51">
-        <v>0.22766666666666666</v>
+        <v>0.22766666666666668</v>
       </c>
       <c r="E51" t="s">
         <v>184</v>
@@ -15662,7 +15662,7 @@
         <v>43</v>
       </c>
       <c r="D57">
-        <v>0.18733333333333335</v>
+        <v>0.18733333333333332</v>
       </c>
       <c r="E57" t="s">
         <v>184</v>
@@ -15718,7 +15718,7 @@
         <v>43</v>
       </c>
       <c r="D61">
-        <v>0.20516666666666664</v>
+        <v>0.20516666666666669</v>
       </c>
       <c r="E61" t="s">
         <v>184</v>
@@ -15774,7 +15774,7 @@
         <v>43</v>
       </c>
       <c r="D65">
-        <v>0.20076666666666665</v>
+        <v>0.20076666666666668</v>
       </c>
       <c r="E65" t="s">
         <v>184</v>
@@ -15886,7 +15886,7 @@
         <v>43</v>
       </c>
       <c r="D73">
-        <v>0.19603333333333331</v>
+        <v>0.19603333333333336</v>
       </c>
       <c r="E73" t="s">
         <v>184</v>
@@ -15942,7 +15942,7 @@
         <v>43</v>
       </c>
       <c r="D77">
-        <v>0.21280000000000002</v>
+        <v>0.21279999999999999</v>
       </c>
       <c r="E77" t="s">
         <v>184</v>
@@ -16138,7 +16138,7 @@
         <v>37</v>
       </c>
       <c r="D91">
-        <v>0.21930000000000002</v>
+        <v>0.21929999999999997</v>
       </c>
       <c r="E91" t="s">
         <v>184</v>
@@ -16530,7 +16530,7 @@
         <v>37</v>
       </c>
       <c r="D119">
-        <v>0.23020000000000004</v>
+        <v>0.23019999999999999</v>
       </c>
       <c r="E119" t="s">
         <v>184</v>
@@ -16614,7 +16614,7 @@
         <v>43</v>
       </c>
       <c r="D125">
-        <v>0.17353333333333332</v>
+        <v>0.17353333333333334</v>
       </c>
       <c r="E125" t="s">
         <v>184</v>

--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_12t.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_12t.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5902694F-C0CB-47B4-9360-B0B81DB2D05F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{72277BA1-4B4B-4ED1-AAAE-03BAA65B327F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -573,10 +573,10 @@
     <t>day_night</t>
   </si>
   <si>
-    <t>FaD,WaP,RaD,SaD,FaP,SaP,WaD,RaP</t>
-  </si>
-  <si>
-    <t>RaP,RaN,WaP,FaP,SaP,FaN,SaN,WaN</t>
+    <t>WaD,FaD,RaP,RaD,SaD,WaP,FaP,SaP</t>
+  </si>
+  <si>
+    <t>WaP,RaP,SaN,WaN,FaP,SaP,FaN,RaN</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>RaP,RaN,WaP,FaP,SaP,FaN,SaN,WaN</v>
+        <v>WaP,RaP,SaN,WaN,FaP,SaP,FaN,RaN</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>FaD,WaP,RaD,SaD,FaP,SaP,WaD,RaP</v>
+        <v>WaD,FaD,RaP,RaD,SaD,WaP,FaP,SaP</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1299,7 +1299,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF976B5A-1238-4615-8F9E-5BDD49EC12DC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58BF2A04-8089-452D-8AF7-58C2A0BEB5F9}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1383,7 +1383,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B748AA6E-5EE5-423F-B76E-A96F768FA63F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22804F55-CC71-455D-9774-CD14E3849A94}">
   <dimension ref="B9:O250"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9125,7 +9125,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2BCB2F5-E8A6-4158-9078-351A5D00BBEF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CAC8E9A-B4CE-4A15-9719-6202D4E2B151}">
   <dimension ref="B9:BL60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14338,7 +14338,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85C25563-88BD-40DF-8909-B448AB7B031E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BCB348F-ACF0-49B4-9427-C1B82E4DC150}">
   <dimension ref="B9:E22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14536,7 +14536,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{472F1561-0FF8-4E78-BC5E-E849DF0C01D4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FCFF391-4399-45FF-ADBF-E41AD1BCC3CD}">
   <dimension ref="B9:D34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14827,7 +14827,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A50453A6-5F68-4A32-B55E-E22932B40C67}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1076ADF5-DCA8-4999-960C-2EBD84B7192C}">
   <dimension ref="B9:D22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14986,7 +14986,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1684FCE-E0FC-4101-85DD-E26C37891A15}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2E324B1-81B7-4FD2-858A-56267DA21C0A}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15116,7 +15116,7 @@
         <v>45</v>
       </c>
       <c r="D18">
-        <v>0.20653333333333332</v>
+        <v>0.20653333333333335</v>
       </c>
       <c r="E18" t="s">
         <v>184</v>
@@ -15158,7 +15158,7 @@
         <v>43</v>
       </c>
       <c r="D21">
-        <v>0.12036666666666666</v>
+        <v>0.12036666666666668</v>
       </c>
       <c r="E21" t="s">
         <v>184</v>
@@ -15564,7 +15564,7 @@
         <v>45</v>
       </c>
       <c r="D50">
-        <v>0.30259999999999998</v>
+        <v>0.30260000000000004</v>
       </c>
       <c r="E50" t="s">
         <v>184</v>
@@ -15718,7 +15718,7 @@
         <v>43</v>
       </c>
       <c r="D61">
-        <v>0.20516666666666664</v>
+        <v>0.20516666666666669</v>
       </c>
       <c r="E61" t="s">
         <v>184</v>
@@ -15732,7 +15732,7 @@
         <v>45</v>
       </c>
       <c r="D62">
-        <v>0.29860000000000003</v>
+        <v>0.29859999999999998</v>
       </c>
       <c r="E62" t="s">
         <v>184</v>
@@ -15844,7 +15844,7 @@
         <v>45</v>
       </c>
       <c r="D70">
-        <v>0.37280000000000002</v>
+        <v>0.37279999999999996</v>
       </c>
       <c r="E70" t="s">
         <v>184</v>
@@ -15886,7 +15886,7 @@
         <v>43</v>
       </c>
       <c r="D73">
-        <v>0.19603333333333331</v>
+        <v>0.19603333333333336</v>
       </c>
       <c r="E73" t="s">
         <v>184</v>
@@ -15942,7 +15942,7 @@
         <v>43</v>
       </c>
       <c r="D77">
-        <v>0.21280000000000002</v>
+        <v>0.21279999999999999</v>
       </c>
       <c r="E77" t="s">
         <v>184</v>
@@ -16012,7 +16012,7 @@
         <v>45</v>
       </c>
       <c r="D82">
-        <v>0.3242666666666667</v>
+        <v>0.32426666666666665</v>
       </c>
       <c r="E82" t="s">
         <v>184</v>
@@ -16068,7 +16068,7 @@
         <v>45</v>
       </c>
       <c r="D86">
-        <v>0.30743333333333334</v>
+        <v>0.30743333333333328</v>
       </c>
       <c r="E86" t="s">
         <v>184</v>
@@ -16180,7 +16180,7 @@
         <v>45</v>
       </c>
       <c r="D94">
-        <v>0.3143333333333333</v>
+        <v>0.31433333333333335</v>
       </c>
       <c r="E94" t="s">
         <v>184</v>
@@ -16334,7 +16334,7 @@
         <v>43</v>
       </c>
       <c r="D105">
-        <v>0.1952666666666667</v>
+        <v>0.19526666666666667</v>
       </c>
       <c r="E105" t="s">
         <v>184</v>
@@ -16460,7 +16460,7 @@
         <v>45</v>
       </c>
       <c r="D114">
-        <v>0.31429999999999997</v>
+        <v>0.31430000000000002</v>
       </c>
       <c r="E114" t="s">
         <v>184</v>
@@ -16572,7 +16572,7 @@
         <v>45</v>
       </c>
       <c r="D122">
-        <v>0.31936666666666663</v>
+        <v>0.31936666666666669</v>
       </c>
       <c r="E122" t="s">
         <v>184</v>
@@ -16614,7 +16614,7 @@
         <v>43</v>
       </c>
       <c r="D125">
-        <v>0.17353333333333332</v>
+        <v>0.17353333333333334</v>
       </c>
       <c r="E125" t="s">
         <v>184</v>

--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_12t.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_12t.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{65938FFD-B3FF-4C7B-BB6B-43A0C8E6892E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{885A0B94-ED53-4389-9B1D-12DACD168356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -576,10 +576,10 @@
     <t>day_night</t>
   </si>
   <si>
-    <t>RaD,FaD,SaD,FaP,SaP,WaD,RaP,WaP</t>
-  </si>
-  <si>
-    <t>SaN,WaN,FaN,RaP,WaP,FaP,SaP,RaN</t>
+    <t>RaP,WaP,FaP,SaP,SaD,WaD,RaD,FaD</t>
+  </si>
+  <si>
+    <t>FaN,WaP,RaN,SaN,WaN,FaP,SaP,RaP</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -864,7 +864,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B58652D5-8646-FA93-9C75-727003D7EBEC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D81A893-FDD3-9A69-696E-5E21DB5DB5FC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -919,7 +919,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B909CC8-2060-DD24-0E8A-B9440AFC8B47}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94F66163-D1BD-CB30-069C-7A6F6FACACB3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -974,7 +974,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5615B3FD-BEA1-20E4-B073-D975D723498A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E41A24F5-E8AD-F155-EB9E-EB1EE11ABF74}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1029,7 +1029,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A851F885-E3A3-F60D-C025-FE81207361F0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{078CA8D8-F5A9-DD97-1256-B5E39A975B70}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1084,7 +1084,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3FE1832B-1736-80C5-77C3-125957B2A5EC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF47C1C6-3D17-C3A4-1523-3C0336F4C87D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1139,7 +1139,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20B6D6D2-FBA2-DEF3-CBA3-391BED290A97}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E9D2BF2-24B2-3518-D421-AC85D2CF021E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1194,7 +1194,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C6871C09-05CF-A2F1-E2FB-E9448899736C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{257B7178-9C2C-00E1-846A-AC67C3327D69}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1249,7 +1249,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3488C5FC-5BDC-7683-E59B-3DF4DE1F3BFA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93615B0C-4DBF-9246-92E6-EF4ACEE5E848}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>SaN,WaN,FaN,RaP,WaP,FaP,SaP,RaN</v>
+        <v>FaN,WaP,RaN,SaN,WaN,FaP,SaP,RaP</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>RaD,FaD,SaD,FaP,SaP,WaD,RaP,WaP</v>
+        <v>RaP,WaP,FaP,SaP,SaD,WaD,RaD,FaD</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1865,7 +1865,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3216D39B-53C8-4FF5-BDF9-807F8A486732}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F12E7441-72ED-45C9-AD52-AFB86C9338A2}">
   <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1976,7 +1976,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB948C98-A5DB-4ED8-947F-9DE42B5308C7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F404EB9F-A303-4C45-8184-A51AC873B523}">
   <dimension ref="A1:O250"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -9742,7 +9742,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAB2C12D-F782-4A71-A7FD-259CF35D2A9C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9343EC1B-3ECB-48A6-A54F-7EB8C59ABBC6}">
   <dimension ref="A1:BL60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -14992,7 +14992,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1075473-ECF1-478C-B5D7-1C92C3C38BE4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFB84500-0C20-4252-8E65-8A1B4456B7E7}">
   <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -15210,7 +15210,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BA1F1A0-F0F2-42D7-802F-A2B0B044EFAD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBBA1950-D306-4167-ACA0-2EED9F50AE26}">
   <dimension ref="A1:H34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -15521,7 +15521,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{944CF082-4453-40EC-A879-893710750520}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{809348FB-5C4F-44F3-AECF-470AFC1D447C}">
   <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -15700,7 +15700,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{389EB901-BC50-42D3-BF59-818924AC329E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F08F34CE-0144-4EE1-ACE5-E04F77A77FED}">
   <dimension ref="A1:H126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -15761,7 +15761,7 @@
         <v>41</v>
       </c>
       <c r="D12" s="24">
-        <v>0.17526666666666665</v>
+        <v>0.17526666666666668</v>
       </c>
       <c r="E12" s="23" t="s">
         <v>185</v>
@@ -15845,7 +15845,7 @@
         <v>45</v>
       </c>
       <c r="D18" s="24">
-        <v>0.20653333333333335</v>
+        <v>0.20653333333333332</v>
       </c>
       <c r="E18" s="23" t="s">
         <v>185</v>
@@ -15873,7 +15873,7 @@
         <v>41</v>
       </c>
       <c r="D20" s="24">
-        <v>0.23150000000000001</v>
+        <v>0.23149999999999996</v>
       </c>
       <c r="E20" s="23" t="s">
         <v>185</v>
@@ -16097,7 +16097,7 @@
         <v>41</v>
       </c>
       <c r="D36" s="24">
-        <v>0.32773333333333338</v>
+        <v>0.32773333333333332</v>
       </c>
       <c r="E36" s="23" t="s">
         <v>185</v>
@@ -16209,7 +16209,7 @@
         <v>41</v>
       </c>
       <c r="D44" s="24">
-        <v>0.34233333333333338</v>
+        <v>0.34233333333333332</v>
       </c>
       <c r="E44" s="23" t="s">
         <v>185</v>
@@ -16293,7 +16293,7 @@
         <v>45</v>
       </c>
       <c r="D50" s="24">
-        <v>0.30260000000000004</v>
+        <v>0.30259999999999998</v>
       </c>
       <c r="E50" s="23" t="s">
         <v>185</v>
@@ -16321,7 +16321,7 @@
         <v>41</v>
       </c>
       <c r="D52" s="24">
-        <v>0.32276666666666665</v>
+        <v>0.3227666666666667</v>
       </c>
       <c r="E52" s="23" t="s">
         <v>185</v>
@@ -16377,7 +16377,7 @@
         <v>41</v>
       </c>
       <c r="D56" s="24">
-        <v>0.35000000000000003</v>
+        <v>0.34999999999999992</v>
       </c>
       <c r="E56" s="23" t="s">
         <v>185</v>
@@ -16461,7 +16461,7 @@
         <v>45</v>
       </c>
       <c r="D62" s="24">
-        <v>0.29859999999999998</v>
+        <v>0.29860000000000003</v>
       </c>
       <c r="E62" s="23" t="s">
         <v>185</v>
@@ -16545,7 +16545,7 @@
         <v>41</v>
       </c>
       <c r="D68" s="24">
-        <v>0.38203333333333328</v>
+        <v>0.38203333333333339</v>
       </c>
       <c r="E68" s="23" t="s">
         <v>185</v>
@@ -16573,7 +16573,7 @@
         <v>45</v>
       </c>
       <c r="D70" s="24">
-        <v>0.37279999999999996</v>
+        <v>0.37280000000000002</v>
       </c>
       <c r="E70" s="23" t="s">
         <v>185</v>
@@ -16741,7 +16741,7 @@
         <v>45</v>
       </c>
       <c r="D82" s="24">
-        <v>0.32426666666666665</v>
+        <v>0.3242666666666667</v>
       </c>
       <c r="E82" s="23" t="s">
         <v>185</v>
@@ -16769,7 +16769,7 @@
         <v>41</v>
       </c>
       <c r="D84" s="24">
-        <v>0.3323666666666667</v>
+        <v>0.33236666666666664</v>
       </c>
       <c r="E84" s="23" t="s">
         <v>185</v>
@@ -16797,7 +16797,7 @@
         <v>45</v>
       </c>
       <c r="D86" s="24">
-        <v>0.30743333333333328</v>
+        <v>0.30743333333333334</v>
       </c>
       <c r="E86" s="23" t="s">
         <v>185</v>
@@ -16881,7 +16881,7 @@
         <v>41</v>
       </c>
       <c r="D92" s="24">
-        <v>0.31546666666666667</v>
+        <v>0.31546666666666673</v>
       </c>
       <c r="E92" s="23" t="s">
         <v>185</v>
@@ -16909,7 +16909,7 @@
         <v>45</v>
       </c>
       <c r="D94" s="24">
-        <v>0.31433333333333335</v>
+        <v>0.3143333333333333</v>
       </c>
       <c r="E94" s="23" t="s">
         <v>185</v>
@@ -17049,7 +17049,7 @@
         <v>41</v>
       </c>
       <c r="D104" s="24">
-        <v>0.32653333333333329</v>
+        <v>0.32653333333333334</v>
       </c>
       <c r="E104" s="23" t="s">
         <v>185</v>
@@ -17105,7 +17105,7 @@
         <v>41</v>
       </c>
       <c r="D108" s="24">
-        <v>0.32569999999999999</v>
+        <v>0.32569999999999993</v>
       </c>
       <c r="E108" s="23" t="s">
         <v>185</v>
@@ -17189,7 +17189,7 @@
         <v>45</v>
       </c>
       <c r="D114" s="24">
-        <v>0.31430000000000002</v>
+        <v>0.31429999999999997</v>
       </c>
       <c r="E114" s="23" t="s">
         <v>185</v>
@@ -17217,7 +17217,7 @@
         <v>41</v>
       </c>
       <c r="D116" s="24">
-        <v>0.32293333333333335</v>
+        <v>0.32293333333333329</v>
       </c>
       <c r="E116" s="23" t="s">
         <v>185</v>
@@ -17301,7 +17301,7 @@
         <v>45</v>
       </c>
       <c r="D122" s="24">
-        <v>0.31936666666666669</v>
+        <v>0.31936666666666663</v>
       </c>
       <c r="E122" s="23" t="s">
         <v>185</v>

--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_12t.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_12t.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A99087F-1DA6-4444-8989-F06847CA1FD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7A5A280C-1263-4647-9938-04188401CCDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -573,10 +573,10 @@
     <t>day_night</t>
   </si>
   <si>
-    <t>SaD,FaD,WaD,RaP,RaD,WaP,FaP,SaP</t>
-  </si>
-  <si>
-    <t>FaP,SaP,WaP,RaP,SaN,WaN,FaN,RaN</t>
+    <t>FaD,RaP,SaD,FaP,SaP,WaP,WaD,RaD</t>
+  </si>
+  <si>
+    <t>FaN,RaP,WaP,FaP,SaP,SaN,WaN,RaN</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>FaP,SaP,WaP,RaP,SaN,WaN,FaN,RaN</v>
+        <v>FaN,RaP,WaP,FaP,SaP,SaN,WaN,RaN</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>SaD,FaD,WaD,RaP,RaD,WaP,FaP,SaP</v>
+        <v>FaD,RaP,SaD,FaP,SaP,WaP,WaD,RaD</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1299,7 +1299,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{900DD9B0-5379-4F9D-A865-1886EBB4A195}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78922DB2-0FC6-48EF-82B9-C686F673640C}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1383,7 +1383,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{456E4600-C9D7-4FFE-8B08-29F6F3484347}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B5AF5E5-6814-4E4B-991C-97A578EEFB94}">
   <dimension ref="B9:O250"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9125,7 +9125,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB6DB3BA-9D86-48C1-A05B-8DF720AD61DA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D6630AB-F465-407E-A85A-BC1D46330DC3}">
   <dimension ref="B9:BL60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14338,7 +14338,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8868297-923E-4F48-8F3E-DC388B874452}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9310CF1-06D0-4378-A223-DFE54F50EEB3}">
   <dimension ref="B9:E22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14536,7 +14536,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0EF4035-F865-40DC-AAB9-83B9E21E2BEE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18A78009-C180-4F96-B983-732DD528F112}">
   <dimension ref="B9:D34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14827,7 +14827,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DE05350-6E97-4B73-A885-F2498F644D35}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D22E2D8-04B1-4524-BFB9-0E7EF62CCBA6}">
   <dimension ref="B9:D22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14986,7 +14986,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EFE1F94-283C-43D6-9549-A6D6BBC0C34C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7446C02A-4040-4FC5-856F-4D89151B0E78}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15172,7 +15172,7 @@
         <v>45</v>
       </c>
       <c r="D22">
-        <v>0.23839999999999997</v>
+        <v>0.23840000000000003</v>
       </c>
       <c r="E22" t="s">
         <v>184</v>
@@ -15564,7 +15564,7 @@
         <v>45</v>
       </c>
       <c r="D50">
-        <v>0.30259999999999998</v>
+        <v>0.30260000000000004</v>
       </c>
       <c r="E50" t="s">
         <v>184</v>
@@ -15620,7 +15620,7 @@
         <v>45</v>
       </c>
       <c r="D54">
-        <v>0.3167666666666667</v>
+        <v>0.31676666666666664</v>
       </c>
       <c r="E54" t="s">
         <v>184</v>
@@ -15732,7 +15732,7 @@
         <v>45</v>
       </c>
       <c r="D62">
-        <v>0.29860000000000003</v>
+        <v>0.29859999999999998</v>
       </c>
       <c r="E62" t="s">
         <v>184</v>
@@ -15844,7 +15844,7 @@
         <v>45</v>
       </c>
       <c r="D70">
-        <v>0.37280000000000002</v>
+        <v>0.37279999999999996</v>
       </c>
       <c r="E70" t="s">
         <v>184</v>
@@ -16348,7 +16348,7 @@
         <v>45</v>
       </c>
       <c r="D106">
-        <v>0.28609999999999997</v>
+        <v>0.28610000000000002</v>
       </c>
       <c r="E106" t="s">
         <v>184</v>
@@ -16404,7 +16404,7 @@
         <v>45</v>
       </c>
       <c r="D110">
-        <v>0.32646666666666668</v>
+        <v>0.32646666666666663</v>
       </c>
       <c r="E110" t="s">
         <v>184</v>
@@ -16572,7 +16572,7 @@
         <v>45</v>
       </c>
       <c r="D122">
-        <v>0.31936666666666663</v>
+        <v>0.31936666666666669</v>
       </c>
       <c r="E122" t="s">
         <v>184</v>
@@ -16628,7 +16628,7 @@
         <v>45</v>
       </c>
       <c r="D126">
-        <v>0.30759999999999998</v>
+        <v>0.30760000000000004</v>
       </c>
       <c r="E126" t="s">
         <v>184</v>

--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_12t.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_12t.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7A5A280C-1263-4647-9938-04188401CCDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AECC12C4-3A21-4818-9B50-393A856863AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -573,10 +573,10 @@
     <t>day_night</t>
   </si>
   <si>
-    <t>FaD,RaP,SaD,FaP,SaP,WaP,WaD,RaD</t>
-  </si>
-  <si>
-    <t>FaN,RaP,WaP,FaP,SaP,SaN,WaN,RaN</t>
+    <t>FaD,FaP,SaP,RaD,RaP,WaD,WaP,SaD</t>
+  </si>
+  <si>
+    <t>RaP,WaP,FaN,RaN,SaN,WaN,FaP,SaP</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>FaN,RaP,WaP,FaP,SaP,SaN,WaN,RaN</v>
+        <v>RaP,WaP,FaN,RaN,SaN,WaN,FaP,SaP</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>FaD,RaP,SaD,FaP,SaP,WaP,WaD,RaD</v>
+        <v>FaD,FaP,SaP,RaD,RaP,WaD,WaP,SaD</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1299,7 +1299,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78922DB2-0FC6-48EF-82B9-C686F673640C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17A48DC1-D04E-4C52-979C-B63B6EDF7680}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1383,7 +1383,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B5AF5E5-6814-4E4B-991C-97A578EEFB94}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56168E3C-BD7C-4B33-850B-5A23B1D4D82E}">
   <dimension ref="B9:O250"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9125,7 +9125,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D6630AB-F465-407E-A85A-BC1D46330DC3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C72C74A-37AC-40CE-83B9-7CEF41338CE5}">
   <dimension ref="B9:BL60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14338,7 +14338,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9310CF1-06D0-4378-A223-DFE54F50EEB3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F431CAA1-B31E-4E30-AB2E-4590F909C65A}">
   <dimension ref="B9:E22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14536,7 +14536,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18A78009-C180-4F96-B983-732DD528F112}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8E3F979-BCF0-4C93-BA1B-B3950919BB47}">
   <dimension ref="B9:D34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14827,7 +14827,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D22E2D8-04B1-4524-BFB9-0E7EF62CCBA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D8FDC02-8B9C-40F2-B1B9-F59C3DE45F7A}">
   <dimension ref="B9:D22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14986,7 +14986,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7446C02A-4040-4FC5-856F-4D89151B0E78}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{618E9FB3-D51A-49BB-A72B-773A448FC8B4}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15032,7 +15032,7 @@
         <v>41</v>
       </c>
       <c r="D12">
-        <v>0.17526666666666665</v>
+        <v>0.17526666666666668</v>
       </c>
       <c r="E12" t="s">
         <v>184</v>
@@ -15116,7 +15116,7 @@
         <v>45</v>
       </c>
       <c r="D18">
-        <v>0.20653333333333335</v>
+        <v>0.20653333333333332</v>
       </c>
       <c r="E18" t="s">
         <v>184</v>
@@ -15564,7 +15564,7 @@
         <v>45</v>
       </c>
       <c r="D50">
-        <v>0.30260000000000004</v>
+        <v>0.30259999999999998</v>
       </c>
       <c r="E50" t="s">
         <v>184</v>
@@ -15592,7 +15592,7 @@
         <v>41</v>
       </c>
       <c r="D52">
-        <v>0.32276666666666665</v>
+        <v>0.3227666666666667</v>
       </c>
       <c r="E52" t="s">
         <v>184</v>
@@ -15732,7 +15732,7 @@
         <v>45</v>
       </c>
       <c r="D62">
-        <v>0.29859999999999998</v>
+        <v>0.29860000000000003</v>
       </c>
       <c r="E62" t="s">
         <v>184</v>
@@ -15760,7 +15760,7 @@
         <v>41</v>
       </c>
       <c r="D64">
-        <v>0.3297666666666666</v>
+        <v>0.32976666666666665</v>
       </c>
       <c r="E64" t="s">
         <v>184</v>
@@ -15844,7 +15844,7 @@
         <v>45</v>
       </c>
       <c r="D70">
-        <v>0.37279999999999996</v>
+        <v>0.37280000000000002</v>
       </c>
       <c r="E70" t="s">
         <v>184</v>
@@ -16012,7 +16012,7 @@
         <v>45</v>
       </c>
       <c r="D82">
-        <v>0.32426666666666665</v>
+        <v>0.3242666666666667</v>
       </c>
       <c r="E82" t="s">
         <v>184</v>
@@ -16068,7 +16068,7 @@
         <v>45</v>
       </c>
       <c r="D86">
-        <v>0.30743333333333328</v>
+        <v>0.30743333333333334</v>
       </c>
       <c r="E86" t="s">
         <v>184</v>
@@ -16152,7 +16152,7 @@
         <v>41</v>
       </c>
       <c r="D92">
-        <v>0.31546666666666667</v>
+        <v>0.31546666666666673</v>
       </c>
       <c r="E92" t="s">
         <v>184</v>
@@ -16180,7 +16180,7 @@
         <v>45</v>
       </c>
       <c r="D94">
-        <v>0.31433333333333335</v>
+        <v>0.3143333333333333</v>
       </c>
       <c r="E94" t="s">
         <v>184</v>
@@ -16376,7 +16376,7 @@
         <v>41</v>
       </c>
       <c r="D108">
-        <v>0.32569999999999999</v>
+        <v>0.32569999999999993</v>
       </c>
       <c r="E108" t="s">
         <v>184</v>
@@ -16460,7 +16460,7 @@
         <v>45</v>
       </c>
       <c r="D114">
-        <v>0.31430000000000002</v>
+        <v>0.31429999999999997</v>
       </c>
       <c r="E114" t="s">
         <v>184</v>
@@ -16572,7 +16572,7 @@
         <v>45</v>
       </c>
       <c r="D122">
-        <v>0.31936666666666669</v>
+        <v>0.31936666666666663</v>
       </c>
       <c r="E122" t="s">
         <v>184</v>
@@ -16600,7 +16600,7 @@
         <v>41</v>
       </c>
       <c r="D124">
-        <v>0.3557333333333334</v>
+        <v>0.35573333333333329</v>
       </c>
       <c r="E124" t="s">
         <v>184</v>

--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_12t.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_12t.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AECC12C4-3A21-4818-9B50-393A856863AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{22692AC1-F33D-4B31-BA79-05A2BB5AC96B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -573,10 +573,10 @@
     <t>day_night</t>
   </si>
   <si>
-    <t>FaD,FaP,SaP,RaD,RaP,WaD,WaP,SaD</t>
-  </si>
-  <si>
-    <t>RaP,WaP,FaN,RaN,SaN,WaN,FaP,SaP</t>
+    <t>SaD,WaP,FaP,SaP,FaD,WaD,RaP,RaD</t>
+  </si>
+  <si>
+    <t>FaP,SaP,SaN,WaN,RaN,RaP,WaP,FaN</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>RaP,WaP,FaN,RaN,SaN,WaN,FaP,SaP</v>
+        <v>FaP,SaP,SaN,WaN,RaN,RaP,WaP,FaN</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>FaD,FaP,SaP,RaD,RaP,WaD,WaP,SaD</v>
+        <v>SaD,WaP,FaP,SaP,FaD,WaD,RaP,RaD</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1299,7 +1299,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17A48DC1-D04E-4C52-979C-B63B6EDF7680}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D44C2EF9-C6C4-4032-964E-31F7853C1B09}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1383,7 +1383,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56168E3C-BD7C-4B33-850B-5A23B1D4D82E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{168BCADB-9EBC-46A8-907E-9E5B09CF1449}">
   <dimension ref="B9:O250"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9125,7 +9125,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C72C74A-37AC-40CE-83B9-7CEF41338CE5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FC76FE9-85E9-4CC4-B17F-807E0809C3A6}">
   <dimension ref="B9:BL60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14338,7 +14338,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F431CAA1-B31E-4E30-AB2E-4590F909C65A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EF782C7-3FFE-47AD-8933-CF79A3173803}">
   <dimension ref="B9:E22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14536,7 +14536,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8E3F979-BCF0-4C93-BA1B-B3950919BB47}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DA20C0A-D76E-49D3-8747-10EE0B360BE2}">
   <dimension ref="B9:D34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14827,7 +14827,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D8FDC02-8B9C-40F2-B1B9-F59C3DE45F7A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7D81E17-59E7-4A9F-AD7B-87DD6ADE3627}">
   <dimension ref="B9:D22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14986,7 +14986,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{618E9FB3-D51A-49BB-A72B-773A448FC8B4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2A0105E-CCD6-441A-8DFC-E1B00B53D991}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15032,7 +15032,7 @@
         <v>41</v>
       </c>
       <c r="D12">
-        <v>0.17526666666666668</v>
+        <v>0.17526666666666665</v>
       </c>
       <c r="E12" t="s">
         <v>184</v>
@@ -15116,7 +15116,7 @@
         <v>45</v>
       </c>
       <c r="D18">
-        <v>0.20653333333333332</v>
+        <v>0.20653333333333335</v>
       </c>
       <c r="E18" t="s">
         <v>184</v>
@@ -15158,7 +15158,7 @@
         <v>43</v>
       </c>
       <c r="D21">
-        <v>0.12036666666666668</v>
+        <v>0.12036666666666666</v>
       </c>
       <c r="E21" t="s">
         <v>184</v>
@@ -15214,7 +15214,7 @@
         <v>43</v>
       </c>
       <c r="D25">
-        <v>0.2446666666666667</v>
+        <v>0.24466666666666667</v>
       </c>
       <c r="E25" t="s">
         <v>184</v>
@@ -15354,7 +15354,7 @@
         <v>37</v>
       </c>
       <c r="D35">
-        <v>0.20660000000000001</v>
+        <v>0.20659999999999998</v>
       </c>
       <c r="E35" t="s">
         <v>184</v>
@@ -15410,7 +15410,7 @@
         <v>37</v>
       </c>
       <c r="D39">
-        <v>0.29533333333333334</v>
+        <v>0.29533333333333339</v>
       </c>
       <c r="E39" t="s">
         <v>184</v>
@@ -15466,7 +15466,7 @@
         <v>37</v>
       </c>
       <c r="D43">
-        <v>0.2288</v>
+        <v>0.22879999999999998</v>
       </c>
       <c r="E43" t="s">
         <v>184</v>
@@ -15522,7 +15522,7 @@
         <v>37</v>
       </c>
       <c r="D47">
-        <v>0.24780000000000002</v>
+        <v>0.24779999999999999</v>
       </c>
       <c r="E47" t="s">
         <v>184</v>
@@ -15564,7 +15564,7 @@
         <v>45</v>
       </c>
       <c r="D50">
-        <v>0.30259999999999998</v>
+        <v>0.30260000000000004</v>
       </c>
       <c r="E50" t="s">
         <v>184</v>
@@ -15578,7 +15578,7 @@
         <v>37</v>
       </c>
       <c r="D51">
-        <v>0.22766666666666666</v>
+        <v>0.22766666666666668</v>
       </c>
       <c r="E51" t="s">
         <v>184</v>
@@ -15592,7 +15592,7 @@
         <v>41</v>
       </c>
       <c r="D52">
-        <v>0.3227666666666667</v>
+        <v>0.32276666666666665</v>
       </c>
       <c r="E52" t="s">
         <v>184</v>
@@ -15662,7 +15662,7 @@
         <v>43</v>
       </c>
       <c r="D57">
-        <v>0.18733333333333335</v>
+        <v>0.18733333333333332</v>
       </c>
       <c r="E57" t="s">
         <v>184</v>
@@ -15732,7 +15732,7 @@
         <v>45</v>
       </c>
       <c r="D62">
-        <v>0.29860000000000003</v>
+        <v>0.29859999999999998</v>
       </c>
       <c r="E62" t="s">
         <v>184</v>
@@ -15746,7 +15746,7 @@
         <v>37</v>
       </c>
       <c r="D63">
-        <v>0.19193333333333337</v>
+        <v>0.19193333333333332</v>
       </c>
       <c r="E63" t="s">
         <v>184</v>
@@ -15760,7 +15760,7 @@
         <v>41</v>
       </c>
       <c r="D64">
-        <v>0.32976666666666665</v>
+        <v>0.3297666666666666</v>
       </c>
       <c r="E64" t="s">
         <v>184</v>
@@ -15774,7 +15774,7 @@
         <v>43</v>
       </c>
       <c r="D65">
-        <v>0.20076666666666665</v>
+        <v>0.20076666666666668</v>
       </c>
       <c r="E65" t="s">
         <v>184</v>
@@ -15802,7 +15802,7 @@
         <v>37</v>
       </c>
       <c r="D67">
-        <v>0.27233333333333332</v>
+        <v>0.27233333333333337</v>
       </c>
       <c r="E67" t="s">
         <v>184</v>
@@ -15844,7 +15844,7 @@
         <v>45</v>
       </c>
       <c r="D70">
-        <v>0.37280000000000002</v>
+        <v>0.37279999999999996</v>
       </c>
       <c r="E70" t="s">
         <v>184</v>
@@ -16012,7 +16012,7 @@
         <v>45</v>
       </c>
       <c r="D82">
-        <v>0.3242666666666667</v>
+        <v>0.32426666666666665</v>
       </c>
       <c r="E82" t="s">
         <v>184</v>
@@ -16068,7 +16068,7 @@
         <v>45</v>
       </c>
       <c r="D86">
-        <v>0.30743333333333334</v>
+        <v>0.30743333333333328</v>
       </c>
       <c r="E86" t="s">
         <v>184</v>
@@ -16138,7 +16138,7 @@
         <v>37</v>
       </c>
       <c r="D91">
-        <v>0.21930000000000002</v>
+        <v>0.21929999999999997</v>
       </c>
       <c r="E91" t="s">
         <v>184</v>
@@ -16152,7 +16152,7 @@
         <v>41</v>
       </c>
       <c r="D92">
-        <v>0.31546666666666673</v>
+        <v>0.31546666666666667</v>
       </c>
       <c r="E92" t="s">
         <v>184</v>
@@ -16180,7 +16180,7 @@
         <v>45</v>
       </c>
       <c r="D94">
-        <v>0.3143333333333333</v>
+        <v>0.31433333333333335</v>
       </c>
       <c r="E94" t="s">
         <v>184</v>
@@ -16306,7 +16306,7 @@
         <v>37</v>
       </c>
       <c r="D103">
-        <v>0.17756666666666668</v>
+        <v>0.17756666666666665</v>
       </c>
       <c r="E103" t="s">
         <v>184</v>
@@ -16334,7 +16334,7 @@
         <v>43</v>
       </c>
       <c r="D105">
-        <v>0.19526666666666667</v>
+        <v>0.1952666666666667</v>
       </c>
       <c r="E105" t="s">
         <v>184</v>
@@ -16376,7 +16376,7 @@
         <v>41</v>
       </c>
       <c r="D108">
-        <v>0.32569999999999993</v>
+        <v>0.32569999999999999</v>
       </c>
       <c r="E108" t="s">
         <v>184</v>
@@ -16460,7 +16460,7 @@
         <v>45</v>
       </c>
       <c r="D114">
-        <v>0.31429999999999997</v>
+        <v>0.31430000000000002</v>
       </c>
       <c r="E114" t="s">
         <v>184</v>
@@ -16572,7 +16572,7 @@
         <v>45</v>
       </c>
       <c r="D122">
-        <v>0.31936666666666663</v>
+        <v>0.31936666666666669</v>
       </c>
       <c r="E122" t="s">
         <v>184</v>
@@ -16586,7 +16586,7 @@
         <v>37</v>
       </c>
       <c r="D123">
-        <v>0.21529999999999996</v>
+        <v>0.21530000000000002</v>
       </c>
       <c r="E123" t="s">
         <v>184</v>
@@ -16600,7 +16600,7 @@
         <v>41</v>
       </c>
       <c r="D124">
-        <v>0.35573333333333329</v>
+        <v>0.3557333333333334</v>
       </c>
       <c r="E124" t="s">
         <v>184</v>
